--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -1181,13 +1181,17 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1195,7 +1199,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Precision=Recall=3/4 nên F1=2PR/(P+R)=0,75.</t>
+          <t>Token F1: Multiset overlap = 3 tokens; candidate = 4 tokens, reference = 4 tokens. Precision = 3/4, Recall = 3/4 =&gt; F1 = 2 * (3/4 * 3/4) / (3/4 + 3/4) = 0,75.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1399,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -1409,7 +1417,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là số từ của reference.</t>
+          <t>Word Error Rate (WER) = (S + D + I) / N_ref = (1 + 0 + 1) / 4 = 2 / 4 = 0,5.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -672,10 +672,26 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Biến “tốt hơn” thành delta và điều kiện reject rõ ràng.
-Phân tích theo nguyên lý thiết kế: Biến “tốt hơn” thành delta và điều kiện reject rõ ràng.</t>
+- 1.0đ: Thiết lập giả thuyết thống kê rõ ràng (Null $H_0$ và Alternative $H_1$) có delta định lượng cụ thể.
+- 1.0đ: Thiết kế giao thức thử nghiệm đối chứng cặp (paired test) trên 300 ca cố định và phân tầng theo 3 risk slices.
+- 1.0đ: Định nghĩa quy tắc bác bỏ (Reject Rule) rõ ràng, có tính phản nghiệm khi vi phạm an toàn.
+- 1.0đ: Đưa ra quy tắc chấp thuận kép (Dual Acceptance Gate: tăng task success và giữ nguyên an toàn).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết lập Giả thuyết Thực nghiệm (Experiment Hypotheses):
+- **Giả thuyết Không ($H_0$ - Null Hypothesis)**: Phiên bản Prompt V2 không làm tăng tỷ lệ thành công tác vụ ($\Delta_{\text{success}} \le 0$) HOẶC làm tăng tỷ lệ vi phạm an toàn trên bất kỳ lát cắt rủi ro nào ($\Delta_{\text{safety\_violation}} &gt; 0$).
+- **Giả thuyết Đối ($H_1$ - Alternative Hypothesis)**: Phiên bản Prompt V2 giúp tăng tỷ lệ thành công tác vụ ít nhất 5 điểm phần trăm ($\Delta_{\text{success}} \ge +5\%$) đồng thời bảo đảm tỷ lệ vi phạm an toàn không tăng ($\Delta_{\text{safety\_violation}} \le 0\%$) trên toàn bộ 3 lát cắt rủi ro (risk slices).
+2. Giao thức Thử nghiệm có Kiểm soát (Controlled Evaluation Protocol):
+- **Thiết kế Đối chứng Cặp (Paired Evaluation Design)**: Chạy song song cả V1 (baseline) và V2 (candidate) trên cùng tập 300 ca thực tế bất biến với cùng seed và `temperature = 0`.
+- **Phân tầng Lát cắt Rủi ro (Stratified Slices)**: 300 ca được phân bổ đều vào 3 lát cắt rủi ro: Lát cắt 1 (Chính sách hoàn tiền phức tạp - 100 ca), Lát cắt 2 (Xử lý khiếu nại gay gắt - 100 ca), và Lát cắt 3 (Dữ liệu cá nhân/bảo mật - 100 ca).
+3. Quy tắc Chấp thuận Bác bỏ được (Falsifiable Acceptance &amp; Rejection Rules):
+- **Quy tắc Bác bỏ (Reject Rule - Tự động Loại bỏ)**: Bác bỏ V2 ngay lập tức nếu xảy ra một trong hai điều kiện:
+  + Tỷ lệ thành công tác vụ tổng thể không đạt mức tăng tối thiểu $+5\%$ với mức ý nghĩa thống kê $p &lt; 0.05$.
+  + Có **BẤT KỲ** ca vi phạm an toàn mới nào phát sinh trên bất kỳ lát cắt nào trong 3 risk slices (Zero Safety Regression Rule: vi phạm ở V2 &gt; V1).
+- **Quy tắc Chấp thuận (Acceptance Rule)**: Chỉ chấp thuận release V2 khi đồng thời thỏa mãn: Tăng trưởng Task Success $\ge 5\%$ VÀ An toàn tuyệt đối trên cả 3 lát cắt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Thử nghiệm Đánh giá (Evaluation Experimentation Principle): Một cuộc thử nghiệm đánh giá Prompt/Model mới không bao giờ được phép đưa ra kết luận chung chung 'V2 cảm giác tốt hơn'. Cần phải định nghĩa giả thuyết có thể bác bỏ (falsifiable hypothesis) với ngưỡng delta định lượng cụ thể. Quan trọng hơn, việc đánh giá trung bình tổng thể thường che giấu sự suy thoái nghiêm trọng tại các phân khúc nhạy cảm; do đó, quy tắc chấp nhận bắt buộc phải áp dụng kiểm định phân tầng (slice-based gate) cho từng lát cắt rủi ro.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Stanford CRFM: Holistic Evaluation of Language Models (HELM, https://crfm.stanford.edu/helm/) &amp; Google SRE Workbook</t>
         </is>
       </c>
     </row>
@@ -758,10 +774,22 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi mode cần nói khi chạy và action gì theo sau.
-Phân tích theo nguyên lý thiết kế: Mỗi mode cần nói khi chạy và action gì theo sau.</t>
+- 1.0đ: Phân vai chuẩn xác cho Nhu cầu 1 (Offline Pre-merge CI, 100% benchmark, block merge action).
+- 1.0đ: Phân vai chuẩn xác cho Nhu cầu 2 (Online Sync Guardrail, 100% traffic, inline blocking action).
+- 1.0đ: Phân vai chuẩn xác cho Nhu cầu 3 (Online Async Eval, 1-5% sampling, alerting/drift action).
+- 1.0đ: Phân vai chuẩn xác cho Nhu cầu 4 (Human-in-the-loop Calibration, targeted sampling ca bất đồng, rubric re-tuning).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân vai Mode, Trigger, Sampling và Action cho 4 Nhu cầu Đánh giá của Trợ lý Y tế (Medical Assistant):
+| Nhu cầu Đánh giá | Chế độ (Mode) | Điểm Kích hoạt (Trigger) | Chiến lược Lấy mẫu (Sampling) | Hành động Theo sau (Action) |
+| :--- | :--- | :--- | :--- | :--- |
+| **1. Kiểm tra hồi quy khi đổi prompt** | **Offline Pre-merge CI Gate** | Kích hoạt khi có Git Pull Request sửa đổi prompt/code. | Chạy trên **100% tập Golden Benchmark cố định** (200-500 ca y khoa chuẩn). | Block merge nếu điểm số thấp hơn baseline; chỉ cho phép merge khi pass 100% test an toàn. |
+| **2. Chặn rò rỉ PII tức thời** | **Online Synchronous Inline Guardrail** | Kích hoạt trên **mọi request thực tế** ngay trước khi model trả kết quả. | Lấy mẫu **100% toàn bộ traffic** (Zero sampling; quét thời gian thực bằng Presidio/Regex). | Chặn đứng phản hồi (Drop/Block), mask thông tin PII, trả thông báo an toàn và kích hoạt PagerDuty cảnh báo khẩn. |
+| **3. Theo dõi drift trên production** | **Online Asynchronous Eval / Monitoring** | Định kỳ hàng giờ/hàng ngày hoặc kích hoạt theo streaming queue. | **Lấy mẫu ngẫu nhiên phân tầng 1 - 5%** traffic sản xuất để tối ưu chi phí. | Cập nhật dashboard xu hướng; nếu phát hiện sụt giảm chất lượng (drift &gt; 5%), phát cảnh báo Warning xem xét lại corpus/prompt. |
+| **4. Hiệu chuẩn Judge khi có bất đồng** | **Human-in-the-Loop Calibration** | Kích hoạt định kỳ hàng tháng hoặc khi tỷ lệ bất đồng giữa các Judge &gt; 10%. | **Lấy mẫu có chủ đích (Targeted Sampling)** 50-100 ca có độ bất đồng cao nhất (low confidence). | Chuyên gia y tế con người gắn nhãn chuẩn (gold labels); hiệu chỉnh lại prompt và rubric của LLM-as-a-Judge. |
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân định Chế độ Đánh giá (Evaluation Mode Architecture): Không có một chế độ đánh giá vạn năng cho mọi tình huống. Chặn PII đòi hỏi tốc độ mili-giây và độ bao phủ 100% inline; kiểm tra hồi quy đòi hỏi tính tất định và chạy trên benchmark tĩnh trước khi release; giám sát drift cần chạy bất đồng bộ để tiết kiệm tài nguyên; và hiệu chuẩn thẩm định viên (Judge Calibration) đòi hỏi sự tham gia sâu của chuyên gia con người trên các ca biên khó (edge cases).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangSmith Evaluation Modes: Pre-production, Production, and Monitoring &amp; Datadog LLM Guardrails Architecture</t>
         </is>
       </c>
     </row>
@@ -844,10 +872,26 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ failure cụ thể chứ không từ metric có sẵn.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ failure cụ thể chứ không từ metric có sẵn.</t>
+- 1.0đ: Mô tả chuẩn xác chế độ thất bại cụ thể (Tool looping inefficiency dù HTTP 200 và kết quả đúng).
+- 1.0đ: Đặt câu hỏi quan sát trực diện vào bản chất vòng lặp công cụ và thời gian lãng phí.
+- 1.0đ: Thiết kế các thước đo định lượng cụ thể (tool redundancy count, trajectory efficiency ratio, P95 duration).
+- 1.0đ: Phân tích thấu đáo các điểm mù của thước đo (phạt oan bài toán khó, không đo được cảm xúc người dùng).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Chuỗi Ánh xạ Thất bại -&gt; Câu hỏi Quan sát -&gt; Thước đo Đo lường (Failure -&gt; Question -&gt; Measure) và Điểm mù:
+1. **Chuỗi Ánh xạ Chuẩn hóa (Failure-to-Metric Mapping)**:
+- **Failure Mode Cụ thể (Chế độ Thất bại Thực tế)**: Agent bị kẹt trong vòng lặp gọi công cụ nhiều lần (Tool Execution Loop / Inefficient Trajectory) khiến thời gian phản hồi kéo dài tới 18 giây, mặc dù câu trả lời cuối cùng đúng chính sách và HTTP trả về 200 OK.
+- **Observable Question (Câu hỏi Quan sát Định lượng)**: 'Trong một phiên làm việc, Agent thực hiện bao nhiêu bước gọi công cụ lặp lại không cần thiết trước khi đưa ra câu trả lời, và thời gian lãng phí cho các bước lặp đó chiếm bao nhiêu phần trăm tổng thời gian tác vụ?'
+- **Concrete Measures (Thước đo Cụ thể)**:
+  + `tool_call_redundancy_count`: Số lần một công cụ được gọi với tham số trùng lặp hoặc không tạo ra thông tin mới trong cùng một session (Ngưỡng cảnh báo: $&gt; 1$).
+  + `trajectory_step_efficiency_ratio`: Tỷ lệ giữa số bước tối ưu lý thuyết ($S_{\text{min}}$) so với số bước thực tế ($S_{\text{actual}}$): $\text{Efficiency} = S_{\text{min}} / S_{\text{actual}}$.
+  + `agent_execution_latency_seconds`: Đo lường thời gian trễ P95/P99 của toàn bộ phiên Agent.
+2. **Điểm mù của Thước đo (Measurement Blind Spots)**:
+- **Đánh tráo Độ trễ với Tính phức tạp Thực sự**: Nếu chỉ đặt thước đo cứng 'thời gian &gt; 15s là lỗi', hệ thống sẽ phạt oan các tác vụ khó thực sự đòi hỏi nhiều bước tra cứu phức tạp hợp lệ.
+- **Bỏ sót Nội dung Câu trả lời**: Thước đo số bước và độ trễ chỉ đo lường tính hiệu quả (efficiency); nó hoàn toàn 'mù' trước việc liệu câu trả lời 18 giây đó có bị thiếu sót sắc thái ngữ cảm hoặc gây ức chế cho người dùng hay không nếu không có thêm metric đo độ hài lòng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy trình Thiết kế Thước đo từ Chế độ Thất bại (Failure-driven Metric Design): Kỹ sư không bao giờ nên bắt đầu từ các metric chung chung có sẵn trong thư viện. Bắt đầu từ một sự cố thực tế (Agent mất 18s do lặp tool), chúng ta đặt câu hỏi trực diện vào cơ chế gây lỗi, từ đó thiết kế ra các chỉ số đặc thù như `tool_redundancy_count` và `trajectory_efficiency`. Đồng thời, luôn phải chỉ ra điểm mù của thước đo để tránh việc tối ưu hóa cục bộ làm tổn hại các tác vụ hợp lệ phức tạp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Workbook: Non-Abstract Large System Design &amp; AgentBench: Evaluating LLMs as Agents (Liu et al., ICLR 2024)</t>
         </is>
       </c>
     </row>
@@ -926,10 +970,28 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Critical state phải được giữ riêng khỏi số điểm cộng dồn.
-Phân tích theo nguyên lý thiết kế: Critical state phải được giữ riêng khỏi số điểm cộng dồn.</t>
+- 1.0đ: Tính đúng điểm Binary Completion: 0 điểm (do thiếu bước hoàn tiền).
+- 1.0đ: Tính đúng điểm Partial Completion (67%) và Weighted Completion (40%).
+- 1.0đ: Lựa chọn chuẩn xác Binary/Critical Gate làm thước đo duy nhất được phép dùng cho cổng release.
+- 1.0đ: Phân tích thấu đáo rủi ro nghiệp vụ nếu dùng điểm cộng dồn (email thông báo hoàn tiền giả mạo khi chưa tạo refund).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. So sánh Ba Phương pháp Chấm điểm Hoàn thành Tác vụ (Task Completion Scoring):
+- **Binary Completion (Hoàn thành Nhị phân: 0 hoặc 1)**:
+  + Quy tắc: Tác vụ chỉ được tính là 1 (Thành công) nếu TẤT CẢ các bước đều hoàn tất hợp lệ; chỉ cần thiếu 1 bước thì tính là 0 (Thất bại).
+  + Áp dụng trong ca này: Bước hoàn tiền ('tạo refund') chưa hề tồn tại trong trace -&gt; **Điểm Binary = 0**.
+- **Partial Completion (Hoàn thành Từng phần Không trọng số)**:
+  + Quy tắc: Đếm số lượng bước hoàn thành chia cho tổng số bước (2 bước hoàn thành / 3 bước tổng thể).
+  + Áp dụng trong ca này: Đã xác minh (bước 1) và gửi email (bước 3) -&gt; **Điểm Partial = 2 / 3 $\approx 0.67$ (67%)**.
+- **Weighted Completion (Hoàn thành Có Trọng số)**:
+  + Quy tắc: Cộng dồn trọng số của các bước đã thực hiện: Xác minh (20%) + Gửi email (20%) = 40%.
+  + Áp dụng trong ca này: **Điểm Weighted = 0.20 + 0.20 = 0.40 (40%)**.
+2. Lựa chọn Điểm số cho Cổng Phát hành (Gate Scoring Decision):
+- **Lựa chọn bắt buộc cho Release Gate**: **BẮT BUỘC SỬ DỤNG Binary Gate kết hợp Điều kiện Tiên quyết Critical Step (Gated Critical Evaluation)**.
+- **Lý giải sâu sắc**: Bước 'tạo refund' là bước cốt lõi mang tính sống còn (Critical State: 60%). Nếu sử dụng điểm Partial (67%) hoặc Weighted (40%) làm điểm trung bình để vượt gate (ví dụ pass threshold = 40%), hệ thống sẽ phê duyệt một con Agent nguy hiểm: **đã gửi email thông báo cho khách là đã hoàn tiền thành công trong khi tiền thực tế chưa hề được hoàn trả**! Do đó, bất kỳ bước Critical nào không hoàn tất thì điểm tổng thể để vượt gate bắt buộc phải quy về **0 (FAIL TẬP TRUNG)**.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Chấm điểm Trạng thái Quyết định (Critical State Preservation in Task Scoring): Trong quy trình nghiệp vụ tài chính hoặc tự động hóa hành động, các bước không có giá trị ngang hàng nhau. Việc cộng dồn điểm số (weighted sum) là một cạm bẫy toán học: nó biến một hành vi gian lận hoặc sai sót nghiêm trọng (nói dối khách hàng qua email) thành một kết quả 'đạt 40% điểm'. Đối với cổng kiểm soát an toàn (Release Gate), trạng thái của bước Critical phải đóng vai trò là chốt chặn phủ quyết (Veto Gate).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SWE-bench: Can Language Models Resolve Real-World GitHub Issues? (Jimenez et al., ICLR 2024) &amp; OpenDevin Evaluation Standards</t>
         </is>
       </c>
     </row>
@@ -1064,10 +1126,25 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng cộng ba metric thành một average xóa mất vai trò.
-Phân tích theo nguyên lý thiết kế: Đừng cộng ba metric thành một average xóa mất vai trò.</t>
+- 1.0đ: Đưa ra quyết định phát hành dứt khoát: REJECT / NO-GO dựa trên vi phạm ngưỡng PII.
+- 1.0đ: Phân tích đúng vai trò của Guardrail Metric như một chốt chặn phủ quyết tuyệt đối (Hard Veto Gate).
+- 1.0đ: Phân tích đúng vai trò của North-Star Metric như mục tiêu tối ưu hóa giá trị người dùng.
+- 1.0đ: Phân tích đúng vai trò của Operational Metric và khẳng định nguyên tắc cấm gộp bình quân xóa nhòa vai trò.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định Phát hành (Release Decision): **REJECT / NO-GO (BÁC BỎ PHÁT HÀNH TUYỆT ĐỐI)**.
+Mặc dù chỉ số North-Star tăng trưởng tốt (+3 điểm) và tỷ lệ lỗi truy vấn rỗng giảm, nhưng phiên bản candidate đã vi phạm trực tiếp rào cản an toàn bất di bất dịch (tỷ lệ rò rỉ PII tăng từ 0% lên 0.2%, vượt ngưỡng trần cho phép là 0%). Do đó, đợt release bị phủ quyết ngay lập tức mà không có ngoại lệ.
+2. Phân định Vai trò của Từng Metric trong Kiến trúc Đánh giá (Eval Metric Role Architecture):
+- **Guardrail Metric (Chỉ số Rào cản An toàn &amp; Pháp lý: PII Leakage)**:
+  + **Vai trò**: Đóng vai trò là **Chốt chặn Phủ quyết Tuyệt đối (Non-negotiable Veto Gate)**. Chỉ số này sở hữu ngưỡng cứng (Hard Threshold = 0%). Bất kỳ sự gia tăng nào lớn hơn 0% đều ngay lập tức hủy bỏ đợt phát hành, bất kể các chỉ số khác tăng trưởng bao nhiêu.
+- **North-Star Metric (Chỉ số Ngôi sao Phương Bắc: Task Success Rate)**:
+  + **Vai trò**: Đóng vai trò là **Mục tiêu Tối ưu hóa Giá trị Nghiệp vụ (Optimization Target)**. Đo lường mức độ hoàn thành nhiệm vụ và giá trị mang lại cho người dùng. Mức tăng +3 điểm là tín hiệu tích cực, nhưng chỉ có ý nghĩa khi Guardrail Metric được thỏa mãn 100%.
+- **Operational / Diagnostic Metric (Chỉ số Vận hành &amp; Chẩn đoán: Retrieval Empty Rate)**:
+  + **Vai trò**: Đóng vai trò là **Chỉ số Sức khỏe Thành phần Hạ tầng (Subsystem Health Indicator)**. Việc empty retrieval giảm chứng minh tầng truy xuất dữ liệu hoạt động hiệu quả hơn, đóng góp vào việc giải thích vì sao Task Success tăng.
+3. **Nguyên tắc Kiến trúc Bất biến**: Tuyệt đối không cộng gộp ba metric thành một điểm số trung bình (composite score), vì phép cộng sẽ xóa sổ vai trò cảnh giới của Guardrail.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiến trúc Thứ bậc Chỉ số Đánh giá (Hierarchical Metric Architecture): Một sai lầm chí mạng trong đánh giá sản phẩm là gộp chung các chỉ số thành một điểm số bình quân có trọng số. Bảo vệ dữ liệu người dùng (PII Guardrail) là nghĩa vụ pháp lý bắt buộc (Zero-tolerance). Nếu gộp chung, mức tăng 3% của Task Success sẽ bù trừ cho mức rò rỉ 0.2% PII, dẫn đến việc release một hệ thống vi phạm luật pháp nghiêm trọng. Guardrail Metric luôn có quyền ưu tiên cao nhất và quyền phủ quyết vô điều kiện.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Embracing Risk &amp; OWASP Top 10 for LLM Applications: LLM06 Excessive Agency / Sensitive Information Disclosure</t>
         </is>
       </c>
     </row>
@@ -1230,10 +1307,30 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mẫu số precision và recall khác nhau.
-Phân tích theo nguyên lý thiết kế: Mẫu số precision và recall khác nhau.</t>
+- 1.0đ: Tính đúng Precision = 3/4 = 0.75 (75%).
+- 1.0đ: Tính đúng Recall = 3/5 = 0.60 (60%).
+- 1.0đ: Áp dụng chuẩn xác công thức trung bình điều hòa tính ra F1 = 2/3 $\approx 0.667$ (66.67%).
+- 1.0đ: Phân tích sâu sắc điều F1 chưa chứng minh (bẫy từ phủ định đảo ngược nghĩa, trật tự từ, sai lệch số liệu).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Precision, Recall và Token F1 Score:
+- Dữ liệu bài toán:
+  + Số lượng token trong tập tham chiếu chuẩn (Reference Multiset): $N_{\text{ref}} = 5$ tokens.
+  + Số lượng token trong câu trả lời ứng viên (Candidate Multiset): $N_{\text{cand}} = 4$ tokens.
+  + Số lượng token giao nhau trùng khớp (Overlap Tokens): $N_{\text{overlap}} = 3$ tokens.
+- **Tính Precision (Độ chính xác)**:
+  $$\text{Precision} = \frac{N_{\text{overlap}}}{N_{\text{cand}}} = \frac{3}{4} = \mathbf{0.75} \quad (75.0\%)$$
+- **Tính Recall (Độ bao phủ)**:
+  $$\text{Recall} = \frac{N_{\text{overlap}}}{N_{\text{ref}}} = \frac{3}{5} = \mathbf{0.60} \quad (60.0\%)$$
+- **Tính Token F1 Score (Trung bình điều hòa giữa Precision và Recall)**:
+  $$\text{F1} = 2 \times \frac{\text{Precision} \times \text{Recall}}{\text{Precision} + \text{Recall}} = 2 \times \frac{0.75 \times 0.60}{0.75 + 0.60} = 2 \times \frac{0.45}{1.35} = \frac{0.90}{1.35} = \frac{2}{3} \approx \mathbf{0.667} \quad (66.67\%)$$
+2. Điều mà Token F1 Score CHƯA chứng minh được (Giới hạn Ngữ nghĩa cốt tử):
+- **Tính Đúng đắn Ngữ nghĩa và Phủ định (Negation Inversion Blind Spot)**: Token F1 chỉ đếm sự trùng lặp từ vựng bề mặt (lexical overlap). Nếu Reference là 'Bệnh nhân **không** được uống thuốc A' và Candidate là 'Bệnh nhân được uống thuốc A', overlap token rất cao (F1 $\approx 0.89$), nhưng về mặt ngữ nghĩa thì hoàn toàn đảo ngược chân lý và gây chết người.
+- **Thứ tự Từ và Ngữ pháp (Word Order &amp; Syntax)**: Token F1 đối xử văn bản như một túi từ (bag of tokens), hoàn toàn không phân biệt được chủ ngữ và vị ngữ ('Chó cắn người' vs 'Người cắn chó' có F1 = 1.0).
+- **Chính xác Thực thể và Số liệu**: Đổi một con số quan trọng (từ $1.000$ thành $9.000$) chỉ làm giảm nhẹ F1 nhưng làm sai lệch hoàn toàn bản chất nghiệp vụ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đánh giá Token Overlap trong NLP (Lexical F1 vs Semantic Correctness): Token F1 là chỉ số truyền thống phổ biến (như trong SQuAD benchmark) để đo lường mức độ trùng khớp từ vựng. Tuy nhiên, sự trùng lặp từ vựng (lexical overlap) không đồng nghĩa với tính đúng đắn ngữ nghĩa (semantic truth). Một câu trả lời có F1 cao ngất ngưởng vẫn có thể là một câu trả lời hoàn toàn sai lệch thực tế do thiếu từ phủ định hoặc hoán đổi vị trí thực thể.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SQuAD: 100,000+ Questions for Machine Comprehension of Text (Rajpurkar et al., EMNLP 2016) &amp; Stanford CS224N</t>
         </is>
       </c>
     </row>
